--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T16:07:52+00:00</t>
+    <t>2026-03-13T19:21:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T19:21:03+00:00</t>
+    <t>2026-03-17T13:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T13:04:13+00:00</t>
+    <t>2026-03-18T17:17:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T17:17:44+00:00</t>
+    <t>2026-03-19T09:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="551">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T09:35:09+00:00</t>
+    <t>2026-06-08T15:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -683,6 +683,10 @@
   </si>
   <si>
     <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ServiceRequestBesoinIdentifierFormat:l'identifiant du besoin doit respecter le format : 3+FINESS/identifiantLocalUsagerESSMS-BESO-numBesoin {value.matches('^3[0-9]{9}/[A-Za-z0-9]+-BESO-[A-Za-z0-9]+$')}</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -4217,7 +4221,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4226,10 +4230,10 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4240,10 +4244,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4266,13 +4270,13 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4323,7 +4327,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4344,10 +4348,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4358,10 +4362,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4384,16 +4388,16 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4443,7 +4447,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4464,10 +4468,10 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4478,10 +4482,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4504,16 +4508,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4563,7 +4567,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4581,13 +4585,13 @@
         <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4598,10 +4602,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4627,13 +4631,13 @@
         <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4683,7 +4687,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4701,13 +4705,13 @@
         <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4718,14 +4722,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4744,13 +4748,13 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4801,7 +4805,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4816,16 +4820,16 @@
         <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -4836,14 +4840,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4862,13 +4866,13 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4919,7 +4923,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4937,13 +4941,13 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4954,14 +4958,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4983,16 +4987,16 @@
         <v>158</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5041,7 +5045,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5059,13 +5063,13 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5076,10 +5080,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5105,13 +5109,13 @@
         <v>112</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5140,10 +5144,10 @@
         <v>184</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5161,7 +5165,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>92</v>
@@ -5179,27 +5183,27 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5225,13 +5229,13 @@
         <v>112</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5260,10 +5264,10 @@
         <v>184</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5281,7 +5285,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>92</v>
@@ -5299,16 +5303,16 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>135</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5316,10 +5320,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5345,16 +5349,16 @@
         <v>190</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5383,7 +5387,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5401,7 +5405,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5416,19 +5420,19 @@
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5436,10 +5440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5465,10 +5469,10 @@
         <v>112</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5476,7 +5480,7 @@
         <v>82</v>
       </c>
       <c r="Q29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="R29" t="s" s="2">
         <v>82</v>
@@ -5500,10 +5504,10 @@
         <v>184</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5521,7 +5525,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5539,16 +5543,16 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5556,10 +5560,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5582,70 +5586,70 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="P30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q30" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="R30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="P30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q30" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="R30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5663,13 +5667,13 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5680,14 +5684,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5709,13 +5713,13 @@
         <v>190</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5741,13 +5745,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5765,7 +5769,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5783,27 +5787,27 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5918,10 +5922,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6038,10 +6042,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6064,19 +6068,19 @@
         <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6125,7 +6129,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6146,10 +6150,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6160,10 +6164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6189,16 +6193,16 @@
         <v>169</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6247,7 +6251,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6262,16 +6266,16 @@
         <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6282,14 +6286,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6311,13 +6315,13 @@
         <v>190</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6343,13 +6347,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6367,7 +6371,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6376,7 +6380,7 @@
         <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
@@ -6388,24 +6392,24 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6520,10 +6524,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6640,10 +6644,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6666,19 +6670,19 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6727,7 +6731,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6748,10 +6752,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6762,10 +6766,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6791,16 +6795,16 @@
         <v>169</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6849,7 +6853,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6864,16 +6868,16 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6884,10 +6888,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6910,17 +6914,17 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6969,7 +6973,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6990,10 +6994,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7004,10 +7008,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7030,13 +7034,13 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7087,7 +7091,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>92</v>
@@ -7105,31 +7109,31 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7148,13 +7152,13 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7205,7 +7209,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7223,31 +7227,31 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7266,13 +7270,13 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7323,7 +7327,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7341,27 +7345,27 @@
         <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7384,13 +7388,13 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7417,13 +7421,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7441,7 +7445,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7465,25 +7469,25 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7502,13 +7506,13 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7559,7 +7563,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7577,31 +7581,31 @@
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7620,16 +7624,16 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7679,7 +7683,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7697,31 +7701,31 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7743,13 +7747,13 @@
         <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7775,13 +7779,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7799,7 +7803,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7817,16 +7821,16 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7834,14 +7838,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7860,16 +7864,16 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7919,7 +7923,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7937,16 +7941,16 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7954,10 +7958,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7983,10 +7987,10 @@
         <v>190</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8013,13 +8017,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8037,7 +8041,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8061,10 +8065,10 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8072,10 +8076,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8098,13 +8102,13 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8155,7 +8159,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8179,10 +8183,10 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8190,10 +8194,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8219,13 +8223,13 @@
         <v>190</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8251,13 +8255,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8275,7 +8279,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8293,16 +8297,16 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8310,10 +8314,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8336,16 +8340,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8395,7 +8399,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8413,16 +8417,16 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8430,10 +8434,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8456,13 +8460,13 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8513,7 +8517,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8531,13 +8535,13 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8548,14 +8552,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8574,16 +8578,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8633,7 +8637,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8651,13 +8655,13 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8668,10 +8672,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8694,16 +8698,16 @@
         <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8753,7 +8757,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8774,10 +8778,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8788,14 +8792,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8817,16 +8821,16 @@
         <v>190</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8851,13 +8855,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8875,7 +8879,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8896,24 +8900,24 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8936,13 +8940,13 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8993,7 +8997,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9011,27 +9015,27 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9146,10 +9150,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9266,10 +9270,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9292,16 +9296,16 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9351,7 +9355,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9375,7 +9379,7 @@
         <v>135</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9386,10 +9390,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9412,13 +9416,13 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9469,7 +9473,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9493,7 +9497,7 @@
         <v>135</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9504,10 +9508,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9530,13 +9534,13 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9587,7 +9591,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>92</v>
@@ -9602,7 +9606,7 @@
         <v>104</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>82</v>
@@ -9611,7 +9615,7 @@
         <v>135</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9622,10 +9626,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9651,10 +9655,10 @@
         <v>169</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9705,7 +9709,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9726,10 +9730,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9740,10 +9744,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9766,16 +9770,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9825,7 +9829,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9843,13 +9847,13 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>135</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2538" uniqueCount="563">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T15:24:46+00:00</t>
+    <t>2026-06-09T07:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -512,31 +512,44 @@
 </t>
   </si>
   <si>
+    <t>Identifiers assigned to this order</t>
+  </si>
+  <si>
+    <t>Identifiers assigned to this order instance by the orderer and/or the receiver and/or order fulfiller.</t>
+  </si>
+  <si>
+    <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 v2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 v2).  For further discussion and examples see the resource notes section below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:type}
+</t>
+  </si>
+  <si>
+    <t>idBesoin</t>
+  </si>
+  <si>
+    <t>Request.identifier</t>
+  </si>
+  <si>
+    <t>ORC.2, ORC.3, RF1-6 / RF1-11,</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>ClinicalStatement.identifier</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin</t>
+  </si>
+  <si>
     <t>Identifiant du besoin</t>
   </si>
   <si>
-    <t>Identifiers assigned to this order instance by the orderer and/or the receiver and/or order fulfiller.</t>
-  </si>
-  <si>
-    <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 v2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 v2).  For further discussion and examples see the resource notes section below.</t>
-  </si>
-  <si>
-    <t>idBesoin</t>
-  </si>
-  <si>
-    <t>Request.identifier</t>
-  </si>
-  <si>
-    <t>ORC.2, ORC.3, RF1-6 / RF1-11,</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>ClinicalStatement.identifier</t>
+    <t>ServiceRequest.identifier:idBesoin.id</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.id</t>
@@ -558,6 +571,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>ServiceRequest.identifier:idBesoin.extension</t>
+  </si>
+  <si>
     <t>ServiceRequest.identifier.extension</t>
   </si>
   <si>
@@ -573,6 +589,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>ServiceRequest.identifier:idBesoin.use</t>
+  </si>
+  <si>
     <t>ServiceRequest.identifier.use</t>
   </si>
   <si>
@@ -601,6 +620,9 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.type</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.type</t>
@@ -622,6 +644,14 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-service-request-besoin-identifier"/&gt;
+    &lt;code value="BES"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -637,6 +667,9 @@
     <t>CX.5</t>
   </si>
   <si>
+    <t>ServiceRequest.identifier:idBesoin.system</t>
+  </si>
+  <si>
     <t>ServiceRequest.identifier.system</t>
   </si>
   <si>
@@ -665,6 +698,9 @@
   </si>
   <si>
     <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.value</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.value</t>
@@ -695,6 +731,9 @@
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
   </si>
   <si>
+    <t>ServiceRequest.identifier:idBesoin.period</t>
+  </si>
+  <si>
     <t>ServiceRequest.identifier.period</t>
   </si>
   <si>
@@ -715,6 +754,9 @@
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.assigner</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.assigner</t>
@@ -2030,10 +2072,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP65"/>
+  <dimension ref="A1:AP66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.8125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="36.125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="30.69921875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="14.828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
@@ -3414,7 +3456,7 @@
         <v>92</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
@@ -3473,16 +3515,14 @@
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>157</v>
@@ -3500,38 +3540,40 @@
         <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>92</v>
@@ -3543,18 +3585,20 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>170</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3603,56 +3647,56 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
@@ -3664,17 +3708,15 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3711,43 +3753,43 @@
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AC14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>82</v>
@@ -3758,33 +3800,33 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>180</v>
@@ -3793,11 +3835,9 @@
         <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -3821,43 +3861,43 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3866,10 +3906,10 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>82</v>
@@ -3880,10 +3920,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3900,25 +3940,25 @@
         <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3943,13 +3983,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3967,7 +4007,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3988,10 +4028,10 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
@@ -4002,10 +4042,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4028,19 +4068,19 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>106</v>
+        <v>197</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -4050,46 +4090,46 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="T17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4110,10 +4150,10 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -4124,10 +4164,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4150,18 +4190,20 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>169</v>
+        <v>106</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
       </c>
@@ -4170,10 +4212,10 @@
         <v>82</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>82</v>
+        <v>214</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>82</v>
@@ -4209,7 +4251,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4221,7 +4263,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>216</v>
+        <v>104</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4247,7 +4289,7 @@
         <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4255,7 +4297,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>92</v>
@@ -4270,7 +4312,7 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>220</v>
+        <v>173</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>221</v>
@@ -4278,7 +4320,9 @@
       <c r="M19" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N19" s="2"/>
+      <c r="N19" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4291,7 +4335,7 @@
         <v>82</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>82</v>
@@ -4327,7 +4371,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4339,7 +4383,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>226</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4348,10 +4392,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4362,10 +4406,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4388,17 +4432,15 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4447,7 +4489,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4468,10 +4510,10 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4482,10 +4524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4496,7 +4538,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4508,16 +4550,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4567,13 +4609,13 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
@@ -4585,13 +4627,13 @@
         <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4602,10 +4644,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4628,16 +4670,16 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>106</v>
+        <v>247</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4687,7 +4729,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4705,13 +4747,13 @@
         <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4722,21 +4764,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4748,15 +4790,17 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>249</v>
+        <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4805,7 +4849,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4820,16 +4864,16 @@
         <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -4840,21 +4884,21 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4866,13 +4910,13 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4923,7 +4967,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4938,16 +4982,16 @@
         <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4958,21 +5002,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4984,20 +5028,16 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>158</v>
+        <v>270</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5045,13 +5085,13 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -5063,13 +5103,13 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5080,18 +5120,18 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>92</v>
@@ -5100,24 +5140,26 @@
         <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5141,13 +5183,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5165,10 +5207,10 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>92</v>
@@ -5183,27 +5225,27 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5229,13 +5271,13 @@
         <v>112</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5261,13 +5303,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5285,7 +5327,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>92</v>
@@ -5303,27 +5345,27 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>135</v>
+        <v>292</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5331,7 +5373,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>92</v>
@@ -5340,26 +5382,24 @@
         <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5383,11 +5423,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5405,13 +5447,13 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
@@ -5420,19 +5462,19 @@
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>300</v>
+        <v>135</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5440,10 +5482,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5466,72 +5508,72 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q29" t="s" s="2">
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Y29" s="2"/>
+      <c r="Z29" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="R29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5540,19 +5582,19 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5560,10 +5602,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5580,76 +5622,72 @@
         <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>313</v>
+        <v>112</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q30" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="R30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="P30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q30" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="R30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5667,16 +5705,16 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>323</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5684,18 +5722,18 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>92</v>
@@ -5704,72 +5742,76 @@
         <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>190</v>
+        <v>325</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M31" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="P31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q31" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="R31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O31" s="2"/>
-      <c r="P31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q31" s="2"/>
-      <c r="R31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5787,35 +5829,35 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>92</v>
@@ -5827,18 +5869,20 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>170</v>
+        <v>335</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5863,13 +5907,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5887,7 +5931,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>172</v>
+        <v>333</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5899,44 +5943,44 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>173</v>
+        <v>343</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5948,17 +5992,15 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M33" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5995,43 +6037,43 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6042,14 +6084,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6065,23 +6107,21 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>337</v>
+        <v>137</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>338</v>
+        <v>180</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>339</v>
+        <v>181</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6117,19 +6157,19 @@
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>342</v>
+        <v>183</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6141,7 +6181,7 @@
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6150,10 +6190,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>344</v>
+        <v>177</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6164,10 +6204,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6175,10 +6215,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6190,19 +6230,19 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>169</v>
+        <v>349</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6251,13 +6291,13 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
@@ -6266,16 +6306,16 @@
         <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6286,21 +6326,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6312,18 +6352,20 @@
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6347,13 +6389,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6371,56 +6413,56 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6429,18 +6471,20 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>170</v>
+        <v>368</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6465,13 +6509,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6489,19 +6533,19 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>172</v>
+        <v>366</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6510,35 +6554,35 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>173</v>
+        <v>343</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6550,17 +6594,15 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M38" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6597,43 +6639,43 @@
         <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AC38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6644,14 +6686,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6667,23 +6709,21 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>337</v>
+        <v>137</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>338</v>
+        <v>180</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>339</v>
+        <v>181</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6719,19 +6759,19 @@
         <v>82</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>342</v>
+        <v>183</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6743,7 +6783,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6752,10 +6792,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>344</v>
+        <v>177</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6766,10 +6806,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6780,7 +6820,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6792,19 +6832,19 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>169</v>
+        <v>349</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6853,13 +6893,13 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
@@ -6868,16 +6908,16 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6888,10 +6928,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6914,17 +6954,19 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>369</v>
+        <v>173</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="O41" t="s" s="2">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6973,7 +7015,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6988,16 +7030,16 @@
         <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7008,10 +7050,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7019,7 +7061,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>92</v>
@@ -7034,16 +7076,18 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7091,10 +7135,10 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>92</v>
@@ -7109,35 +7153,35 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>92</v>
@@ -7152,13 +7196,13 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7209,10 +7253,10 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>92</v>
@@ -7227,31 +7271,31 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7270,13 +7314,13 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7327,7 +7371,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7345,31 +7389,31 @@
         <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7388,13 +7432,13 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7421,13 +7465,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7445,7 +7489,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7463,31 +7507,31 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7506,13 +7550,13 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7539,13 +7583,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7563,7 +7607,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7581,31 +7625,31 @@
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7624,17 +7668,15 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7683,7 +7725,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7701,31 +7743,31 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7744,16 +7786,16 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>190</v>
+        <v>435</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7779,13 +7821,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7803,7 +7845,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7833,26 +7875,26 @@
         <v>442</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7864,7 +7906,7 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>445</v>
+        <v>197</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>446</v>
@@ -7899,13 +7941,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7923,13 +7965,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -7941,16 +7983,16 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7958,14 +8000,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7984,15 +8026,17 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>190</v>
+        <v>457</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8017,31 +8061,31 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8059,16 +8103,16 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>82</v>
+        <v>462</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8076,10 +8120,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8102,13 +8146,13 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>459</v>
+        <v>197</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8135,13 +8179,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8159,7 +8203,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8183,10 +8227,10 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8194,10 +8238,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8220,17 +8264,15 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>190</v>
+        <v>471</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8255,13 +8297,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>467</v>
+        <v>82</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8279,7 +8321,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8297,16 +8339,16 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>468</v>
+        <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>469</v>
+        <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8314,10 +8356,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8340,16 +8382,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>473</v>
+        <v>197</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8375,13 +8417,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8399,7 +8441,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8417,16 +8459,16 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8434,10 +8476,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8457,18 +8499,20 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8517,7 +8561,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8535,16 +8579,16 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>82</v>
+        <v>483</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8552,14 +8596,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>488</v>
+        <v>82</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8578,17 +8622,15 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8637,7 +8679,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8655,13 +8697,13 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8672,14 +8714,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>500</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8695,19 +8737,19 @@
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8757,7 +8799,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8775,13 +8817,13 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8792,14 +8834,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8818,20 +8860,18 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>190</v>
+        <v>509</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -8855,13 +8895,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8879,7 +8919,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8900,28 +8940,28 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>512</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8937,19 +8977,23 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>514</v>
+        <v>197</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>50</v>
+        <v>517</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -8973,13 +9017,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -8997,7 +9041,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9015,27 +9059,27 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>362</v>
+        <v>513</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9046,7 +9090,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9058,13 +9102,13 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>169</v>
+        <v>526</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>171</v>
+        <v>527</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9115,56 +9159,56 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>172</v>
+        <v>525</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>173</v>
+        <v>529</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9176,17 +9220,15 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9223,43 +9265,43 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9270,21 +9312,21 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9293,19 +9335,19 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>522</v>
+        <v>137</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>523</v>
+        <v>180</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>524</v>
+        <v>181</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>525</v>
+        <v>154</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9343,31 +9385,31 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>526</v>
+        <v>183</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9376,10 +9418,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>527</v>
+        <v>177</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9390,10 +9432,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9416,15 +9458,17 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>413</v>
+        <v>534</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9473,7 +9517,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9497,7 +9541,7 @@
         <v>135</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9508,10 +9552,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9519,7 +9563,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>92</v>
@@ -9534,13 +9578,13 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>534</v>
+        <v>425</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9591,10 +9635,10 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>92</v>
@@ -9606,7 +9650,7 @@
         <v>104</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>538</v>
+        <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>82</v>
@@ -9615,7 +9659,7 @@
         <v>135</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9626,10 +9670,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9637,7 +9681,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>92</v>
@@ -9652,13 +9696,13 @@
         <v>93</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>169</v>
+        <v>546</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9709,10 +9753,10 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>92</v>
@@ -9724,16 +9768,16 @@
         <v>104</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>362</v>
+        <v>135</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9744,10 +9788,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9758,7 +9802,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9767,20 +9811,18 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>545</v>
+        <v>173</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>548</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9829,13 +9871,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -9847,18 +9889,138 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="AN65" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP65" t="s" s="2">
+      <c r="AN66" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T07:55:39+00:00</t>
+    <t>2026-06-09T09:58:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -646,7 +646,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-service-request-besoin-identifier"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-service-request-identifier"/&gt;
     &lt;code value="BES"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T09:58:53+00:00</t>
+    <t>2026-06-10T14:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T14:13:27+00:00</t>
+    <t>2026-06-12T15:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:13:13+00:00</t>
+    <t>2026-06-15T13:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T13:25:13+00:00</t>
+    <t>2026-06-16T07:36:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T07:36:31+00:00</t>
+    <t>2026-06-16T07:55:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T07:55:16+00:00</t>
+    <t>2026-06-16T08:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:15:37+00:00</t>
+    <t>2026-06-17T09:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:17:48+00:00</t>
+    <t>2026-06-17T09:36:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:36:47+00:00</t>
+    <t>2026-06-19T10:27:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2538" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2841" uniqueCount="561">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T10:27:30+00:00</t>
+    <t>2026-06-22T09:32:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,15 +543,6 @@
     <t>ClinicalStatement.identifier</t>
   </si>
   <si>
-    <t>ServiceRequest.identifier:idBesoin</t>
-  </si>
-  <si>
-    <t>Identifiant du besoin</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:idBesoin.id</t>
-  </si>
-  <si>
     <t>ServiceRequest.identifier.id</t>
   </si>
   <si>
@@ -571,9 +562,6 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>ServiceRequest.identifier:idBesoin.extension</t>
-  </si>
-  <si>
     <t>ServiceRequest.identifier.extension</t>
   </si>
   <si>
@@ -589,9 +577,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ServiceRequest.identifier:idBesoin.use</t>
-  </si>
-  <si>
     <t>ServiceRequest.identifier.use</t>
   </si>
   <si>
@@ -620,9 +605,6 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:idBesoin.type</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.type</t>
@@ -642,6 +624,131 @@
   </si>
   <si>
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-service-request-identifier-besoin</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin</t>
+  </si>
+  <si>
+    <t>Identifiant du besoin</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.use</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.type</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -652,136 +759,23 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
     <t>ServiceRequest.identifier:idBesoin.system</t>
   </si>
   <si>
-    <t>ServiceRequest.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
     <t>https://identifiant-medicosocial-besoin.esante.gouv.fr</t>
   </si>
   <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
     <t>ServiceRequest.identifier:idBesoin.value</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ServiceRequestBesoinIdentifierFormat:l'identifiant du besoin doit respecter le format : 3+FINESS/identifiantLocalUsagerESSMS-BESO-numBesoin {value.matches('^3[0-9]{9}/[A-Za-z0-9]+-BESO-[A-Za-z0-9]+$')}</t>
   </si>
   <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
     <t>ServiceRequest.identifier:idBesoin.period</t>
   </si>
   <si>
-    <t>ServiceRequest.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
     <t>ServiceRequest.identifier:idBesoin.assigner</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
   </si>
   <si>
     <t>ServiceRequest.instantiatesCanonical</t>
@@ -2072,7 +2066,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP66"/>
+  <dimension ref="A1:AP74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.125" customWidth="true" bestFit="true"/>
@@ -3563,17 +3557,15 @@
         <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>92</v>
@@ -3585,20 +3577,18 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3647,56 +3637,56 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
@@ -3708,15 +3698,17 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3753,31 +3745,31 @@
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>82</v>
@@ -3789,7 +3781,7 @@
         <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>82</v>
@@ -3800,44 +3792,46 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -3861,43 +3855,43 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3906,10 +3900,10 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>82</v>
@@ -3920,10 +3914,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3940,25 +3934,25 @@
         <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>112</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3983,13 +3977,11 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4007,7 +3999,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4028,10 +4020,10 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
@@ -4042,10 +4034,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4053,7 +4045,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>92</v>
@@ -4068,19 +4060,19 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>197</v>
+        <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -4090,10 +4082,10 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>202</v>
+        <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>82</v>
@@ -4105,31 +4097,31 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="Z17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4150,10 +4142,10 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -4167,7 +4159,7 @@
         <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4175,7 +4167,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>92</v>
@@ -4190,20 +4182,18 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N18" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>213</v>
-      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
       </c>
@@ -4212,10 +4202,10 @@
         <v>82</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>82</v>
@@ -4251,7 +4241,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4272,10 +4262,10 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4286,10 +4276,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4297,7 +4287,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>92</v>
@@ -4312,17 +4302,15 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4335,7 +4323,7 @@
         <v>82</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>82</v>
@@ -4371,7 +4359,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4383,7 +4371,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>226</v>
+        <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4392,10 +4380,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4406,10 +4394,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4432,15 +4420,17 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4489,7 +4479,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4510,10 +4500,10 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4524,18 +4514,20 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>92</v>
@@ -4550,16 +4542,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>239</v>
+        <v>158</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>242</v>
+        <v>161</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4609,13 +4601,13 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>243</v>
+        <v>157</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
@@ -4627,27 +4619,27 @@
         <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>244</v>
+        <v>165</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>245</v>
+        <v>166</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>169</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4658,7 +4650,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4667,20 +4659,18 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>247</v>
+        <v>170</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>248</v>
+        <v>171</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4729,31 +4719,31 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>246</v>
+        <v>173</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>253</v>
+        <v>174</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4764,14 +4754,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>254</v>
+        <v>175</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4787,19 +4777,19 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>255</v>
+        <v>176</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>256</v>
+        <v>177</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4837,19 +4827,19 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>254</v>
+        <v>179</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4861,19 +4851,19 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>253</v>
+        <v>174</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -4884,18 +4874,18 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>260</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>92</v>
@@ -4904,22 +4894,26 @@
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>261</v>
+        <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>262</v>
+        <v>181</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4943,13 +4937,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4967,13 +4961,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -4982,16 +4976,16 @@
         <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>266</v>
+        <v>135</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>267</v>
+        <v>189</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5002,21 +4996,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>268</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -5028,16 +5022,20 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>270</v>
+        <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>192</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5046,7 +5044,7 @@
         <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>82</v>
@@ -5061,13 +5059,11 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5085,13 +5081,13 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>268</v>
+        <v>197</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -5103,13 +5099,13 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>274</v>
+        <v>198</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>275</v>
+        <v>189</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5120,18 +5116,18 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>276</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>276</v>
+        <v>199</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>92</v>
@@ -5146,19 +5142,19 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>278</v>
+        <v>200</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>279</v>
+        <v>201</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>280</v>
+        <v>202</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>281</v>
+        <v>203</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5168,10 +5164,10 @@
         <v>82</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>82</v>
@@ -5207,7 +5203,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>205</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5225,13 +5221,13 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>283</v>
+        <v>206</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>284</v>
+        <v>207</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5242,10 +5238,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>285</v>
+        <v>208</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5262,22 +5258,22 @@
         <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>286</v>
+        <v>209</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>287</v>
+        <v>210</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>288</v>
+        <v>211</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5291,7 +5287,7 @@
         <v>82</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>82</v>
@@ -5303,13 +5299,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5327,10 +5323,10 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>285</v>
+        <v>213</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>92</v>
@@ -5339,33 +5335,33 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>292</v>
+        <v>214</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>293</v>
+        <v>215</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>296</v>
+        <v>216</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5373,7 +5369,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>92</v>
@@ -5382,23 +5378,21 @@
         <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>112</v>
+        <v>217</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5423,13 +5417,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5447,10 +5441,10 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>92</v>
@@ -5465,16 +5459,16 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>303</v>
+        <v>222</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5482,10 +5476,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>305</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>305</v>
+        <v>223</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5508,20 +5502,18 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>306</v>
+        <v>225</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>307</v>
+        <v>226</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5545,11 +5537,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5567,13 +5561,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5582,19 +5576,19 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>312</v>
+        <v>229</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>313</v>
+        <v>230</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5602,10 +5596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>314</v>
+        <v>244</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>314</v>
+        <v>244</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5616,7 +5610,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5628,22 +5622,22 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>112</v>
+        <v>245</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>315</v>
+        <v>246</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q30" t="s" s="2">
-        <v>317</v>
-      </c>
+      <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5663,13 +5657,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5687,13 +5681,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>314</v>
+        <v>244</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5705,16 +5699,16 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>320</v>
+        <v>249</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>321</v>
+        <v>250</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>322</v>
+        <v>251</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5722,10 +5716,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5736,38 +5730,34 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>325</v>
+        <v>106</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>326</v>
+        <v>253</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>327</v>
+        <v>254</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q31" t="s" s="2">
-        <v>330</v>
-      </c>
+      <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5811,13 +5801,13 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
@@ -5829,13 +5819,13 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>331</v>
+        <v>256</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>332</v>
+        <v>251</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5846,14 +5836,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>333</v>
+        <v>257</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>333</v>
+        <v>257</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>334</v>
+        <v>258</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5872,17 +5862,15 @@
         <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>197</v>
+        <v>259</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>335</v>
+        <v>260</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5907,13 +5895,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>339</v>
+        <v>82</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>340</v>
+        <v>82</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5931,13 +5919,13 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>333</v>
+        <v>257</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
@@ -5946,41 +5934,41 @@
         <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>341</v>
+        <v>263</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>342</v>
+        <v>264</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>343</v>
+        <v>265</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>346</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>346</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5989,16 +5977,16 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>173</v>
+        <v>268</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>174</v>
+        <v>269</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>175</v>
+        <v>270</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6049,31 +6037,31 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>176</v>
+        <v>266</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>177</v>
+        <v>273</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6084,21 +6072,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>347</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>347</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>151</v>
+        <v>275</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -6107,21 +6095,23 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>180</v>
+        <v>276</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>181</v>
+        <v>277</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6157,43 +6147,43 @@
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>183</v>
+        <v>274</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>177</v>
+        <v>282</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6204,10 +6194,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>348</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>348</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6215,35 +6205,33 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>349</v>
+        <v>112</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>350</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>351</v>
+        <v>285</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6267,13 +6255,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6291,13 +6279,13 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>354</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
@@ -6309,27 +6297,27 @@
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>355</v>
+        <v>290</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>356</v>
+        <v>291</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>357</v>
+        <v>294</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>357</v>
+        <v>294</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6346,26 +6334,24 @@
         <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>358</v>
+        <v>295</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>359</v>
+        <v>296</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6389,13 +6375,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6413,10 +6399,10 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>362</v>
+        <v>294</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>92</v>
@@ -6428,19 +6414,19 @@
         <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>364</v>
+        <v>135</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>365</v>
+        <v>301</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6448,21 +6434,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>366</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>366</v>
+        <v>303</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6474,18 +6460,20 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>368</v>
+        <v>304</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>369</v>
+        <v>305</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6509,13 +6497,11 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>372</v>
+        <v>308</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6533,7 +6519,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>366</v>
+        <v>303</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6542,36 +6528,36 @@
         <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>374</v>
+        <v>310</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>343</v>
+        <v>311</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>375</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>375</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6591,23 +6577,25 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>174</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q38" s="2"/>
+      <c r="Q38" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="R38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6627,13 +6615,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6651,7 +6639,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>176</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6663,22 +6651,22 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>177</v>
+        <v>320</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6686,48 +6674,52 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>376</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>376</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>137</v>
+        <v>323</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>180</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>181</v>
+        <v>325</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q39" s="2"/>
+      <c r="Q39" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="R39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6759,43 +6751,43 @@
         <v>82</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>183</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>177</v>
+        <v>330</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6806,21 +6798,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>377</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>377</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6832,20 +6824,18 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>349</v>
+        <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6869,13 +6859,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6893,13 +6883,13 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
@@ -6911,27 +6901,27 @@
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>378</v>
+        <v>344</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>378</v>
+        <v>344</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6951,23 +6941,19 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>358</v>
+        <v>171</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7015,7 +7001,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>362</v>
+        <v>173</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7027,19 +7013,19 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>379</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>365</v>
+        <v>174</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7050,21 +7036,21 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>380</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>345</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7073,21 +7059,21 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>381</v>
+        <v>137</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>382</v>
+        <v>176</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7123,31 +7109,31 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>380</v>
+        <v>179</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7156,10 +7142,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>385</v>
+        <v>174</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7170,10 +7156,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>386</v>
+        <v>346</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>386</v>
+        <v>346</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7181,10 +7167,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7196,16 +7182,20 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>387</v>
+        <v>347</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>388</v>
+        <v>348</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7253,13 +7243,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7271,35 +7261,35 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>391</v>
+        <v>353</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>392</v>
+        <v>354</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>394</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>395</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>395</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>92</v>
@@ -7314,16 +7304,20 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>397</v>
+        <v>170</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>398</v>
+        <v>356</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7371,7 +7365,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>395</v>
+        <v>360</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7386,41 +7380,41 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>401</v>
+        <v>362</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>402</v>
+        <v>363</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>405</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>405</v>
+        <v>364</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>406</v>
+        <v>365</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7432,15 +7426,17 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>407</v>
+        <v>191</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>408</v>
+        <v>366</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7465,13 +7461,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7489,16 +7485,16 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>405</v>
+        <v>364</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>104</v>
@@ -7507,27 +7503,27 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>411</v>
+        <v>372</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>412</v>
+        <v>341</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>414</v>
+        <v>343</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>415</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>415</v>
+        <v>373</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7547,16 +7543,16 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>416</v>
+        <v>170</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>417</v>
+        <v>171</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>418</v>
+        <v>172</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7583,13 +7579,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7607,7 +7603,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>415</v>
+        <v>173</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7619,7 +7615,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7631,32 +7627,32 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>421</v>
+        <v>174</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>423</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>423</v>
+        <v>374</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>424</v>
+        <v>151</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7665,18 +7661,20 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>425</v>
+        <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>426</v>
+        <v>176</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7713,68 +7711,68 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>423</v>
+        <v>179</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>430</v>
+        <v>174</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>433</v>
+        <v>375</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>433</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7786,18 +7784,20 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>435</v>
+        <v>347</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>436</v>
+        <v>348</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>437</v>
+        <v>349</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7845,13 +7845,13 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>433</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -7863,31 +7863,31 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>441</v>
+        <v>354</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>444</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>444</v>
+        <v>376</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7906,18 +7906,20 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>446</v>
+        <v>356</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>447</v>
+        <v>357</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7941,13 +7943,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7965,7 +7967,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>444</v>
+        <v>360</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7980,19 +7982,19 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>452</v>
+        <v>362</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>453</v>
+        <v>363</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8000,21 +8002,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>455</v>
+        <v>378</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>455</v>
+        <v>378</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8026,18 +8028,18 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>457</v>
+        <v>379</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>458</v>
+        <v>380</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8085,13 +8087,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>455</v>
+        <v>378</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -8103,16 +8105,16 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>461</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>462</v>
+        <v>372</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>463</v>
+        <v>383</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8120,10 +8122,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>464</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>464</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8131,10 +8133,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8146,13 +8148,13 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>197</v>
+        <v>385</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>465</v>
+        <v>386</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>466</v>
+        <v>387</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8179,13 +8181,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>467</v>
+        <v>82</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>468</v>
+        <v>82</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8203,13 +8205,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>464</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -8221,38 +8223,38 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>469</v>
+        <v>390</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>454</v>
+        <v>391</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>470</v>
+        <v>393</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>470</v>
+        <v>393</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8264,13 +8266,13 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>471</v>
+        <v>395</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>465</v>
+        <v>396</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>472</v>
+        <v>397</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8321,13 +8323,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>470</v>
+        <v>393</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8339,38 +8341,38 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>473</v>
+        <v>400</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>454</v>
+        <v>401</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>82</v>
+        <v>402</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>474</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>474</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8382,17 +8384,15 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>197</v>
+        <v>405</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>475</v>
+        <v>406</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8417,13 +8417,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>478</v>
+        <v>82</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8441,13 +8441,13 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>474</v>
+        <v>403</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
@@ -8459,27 +8459,27 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>480</v>
+        <v>408</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>481</v>
+        <v>409</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>482</v>
+        <v>410</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>483</v>
+        <v>411</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>484</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>484</v>
+        <v>413</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8490,7 +8490,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8502,17 +8502,15 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>485</v>
+        <v>414</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>486</v>
+        <v>415</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8537,13 +8535,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8561,13 +8559,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>484</v>
+        <v>413</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -8579,38 +8577,38 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>491</v>
+        <v>419</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>492</v>
+        <v>421</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>492</v>
+        <v>421</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8619,16 +8617,16 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>493</v>
+        <v>423</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>494</v>
+        <v>424</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>495</v>
+        <v>425</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8679,13 +8677,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>492</v>
+        <v>421</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -8697,38 +8695,38 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>496</v>
+        <v>426</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>497</v>
+        <v>427</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>498</v>
+        <v>428</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>499</v>
+        <v>431</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>499</v>
+        <v>431</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>500</v>
+        <v>432</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8737,19 +8735,19 @@
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>501</v>
+        <v>433</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>502</v>
+        <v>434</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>503</v>
+        <v>435</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>504</v>
+        <v>436</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8799,13 +8797,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>499</v>
+        <v>431</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -8817,38 +8815,38 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>505</v>
+        <v>437</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>506</v>
+        <v>438</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>507</v>
+        <v>439</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>508</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>508</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8860,16 +8858,16 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>509</v>
+        <v>191</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>510</v>
+        <v>444</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>511</v>
+        <v>445</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>512</v>
+        <v>446</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8895,13 +8893,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>82</v>
+        <v>447</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8919,13 +8917,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>508</v>
+        <v>442</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -8937,16 +8935,16 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>513</v>
+        <v>450</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>514</v>
+        <v>451</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -8954,14 +8952,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>515</v>
+        <v>453</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>515</v>
+        <v>453</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>516</v>
+        <v>454</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8980,20 +8978,18 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>197</v>
+        <v>455</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>517</v>
+        <v>456</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>518</v>
+        <v>457</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9017,13 +9013,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9041,7 +9037,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>515</v>
+        <v>453</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9059,27 +9055,27 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>513</v>
+        <v>460</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>523</v>
+        <v>461</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>524</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>525</v>
+        <v>462</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>525</v>
+        <v>462</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9099,16 +9095,16 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>526</v>
+        <v>191</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>50</v>
+        <v>463</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>527</v>
+        <v>464</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9135,13 +9131,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>82</v>
+        <v>465</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9159,7 +9155,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>525</v>
+        <v>462</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9177,27 +9173,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>529</v>
+        <v>467</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>531</v>
+        <v>468</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>531</v>
+        <v>468</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9208,7 +9204,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9217,16 +9213,16 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>173</v>
+        <v>469</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>174</v>
+        <v>463</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>175</v>
+        <v>470</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9277,19 +9273,19 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>176</v>
+        <v>468</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9301,10 +9297,10 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>177</v>
+        <v>471</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9312,14 +9308,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>532</v>
+        <v>472</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>532</v>
+        <v>472</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9335,19 +9331,19 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>137</v>
+        <v>191</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>180</v>
+        <v>473</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>181</v>
+        <v>474</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>154</v>
+        <v>475</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9373,31 +9369,31 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>82</v>
+        <v>476</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>183</v>
+        <v>472</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9409,22 +9405,22 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>177</v>
+        <v>480</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9432,10 +9428,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>533</v>
+        <v>482</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>533</v>
+        <v>482</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9446,7 +9442,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9458,16 +9454,16 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>534</v>
+        <v>483</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>535</v>
+        <v>484</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>536</v>
+        <v>485</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>537</v>
+        <v>486</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9517,13 +9513,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>538</v>
+        <v>482</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -9535,16 +9531,16 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>82</v>
+        <v>487</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>135</v>
+        <v>488</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>539</v>
+        <v>489</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
@@ -9552,10 +9548,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9566,7 +9562,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9575,16 +9571,16 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>425</v>
+        <v>491</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>541</v>
+        <v>492</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>542</v>
+        <v>493</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9635,13 +9631,13 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>543</v>
+        <v>490</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
@@ -9653,13 +9649,13 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>135</v>
+        <v>495</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>544</v>
+        <v>496</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9670,21 +9666,21 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>545</v>
+        <v>497</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>545</v>
+        <v>497</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9693,18 +9689,20 @@
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>546</v>
+        <v>499</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>547</v>
+        <v>500</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9753,13 +9751,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>549</v>
+        <v>497</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -9768,16 +9766,16 @@
         <v>104</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>550</v>
+        <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>135</v>
+        <v>504</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>551</v>
+        <v>505</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9788,10 +9786,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>552</v>
+        <v>506</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>552</v>
+        <v>506</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9802,7 +9800,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9814,15 +9812,17 @@
         <v>93</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>173</v>
+        <v>507</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>553</v>
+        <v>508</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9871,13 +9871,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>552</v>
+        <v>506</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -9892,10 +9892,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>374</v>
+        <v>511</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>555</v>
+        <v>512</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -9906,14 +9906,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>556</v>
+        <v>513</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>556</v>
+        <v>513</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>82</v>
+        <v>514</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9929,21 +9929,23 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>557</v>
+        <v>191</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>558</v>
+        <v>515</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>559</v>
+        <v>516</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -9967,13 +9969,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -9991,7 +9993,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>556</v>
+        <v>513</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10009,18 +10011,968 @@
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>561</v>
+        <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="AN66" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP66" t="s" s="2">
+      <c r="AN70" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:32:11+00:00</t>
+    <t>2026-06-24T08:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -525,9 +525,6 @@
 </t>
   </si>
   <si>
-    <t>idBesoin</t>
-  </si>
-  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -734,6 +731,9 @@
   </si>
   <si>
     <t>ServiceRequest.identifier:idBesoin</t>
+  </si>
+  <si>
+    <t>idBesoin</t>
   </si>
   <si>
     <t>Identifiant du besoin</t>
@@ -3534,30 +3534,30 @@
         <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AO12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>168</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3580,13 +3580,13 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3637,7 +3637,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3661,7 +3661,7 @@
         <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3672,10 +3672,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3701,10 +3701,10 @@
         <v>137</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>154</v>
@@ -3748,7 +3748,7 @@
         <v>140</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
@@ -3757,7 +3757,7 @@
         <v>141</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3781,7 +3781,7 @@
         <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>82</v>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3821,16 +3821,16 @@
         <v>112</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3855,31 +3855,31 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3903,7 +3903,7 @@
         <v>135</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>82</v>
@@ -3914,10 +3914,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3940,19 +3940,19 @@
         <v>93</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3977,29 +3977,29 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4020,10 +4020,10 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
@@ -4034,10 +4034,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4063,16 +4063,16 @@
         <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -4085,43 +4085,43 @@
         <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4142,10 +4142,10 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -4156,10 +4156,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4182,16 +4182,16 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4205,43 +4205,43 @@
         <v>82</v>
       </c>
       <c r="T18" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4262,10 +4262,10 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4276,10 +4276,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4302,13 +4302,13 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4359,7 +4359,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4380,10 +4380,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4394,10 +4394,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4420,16 +4420,16 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4479,7 +4479,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4500,10 +4500,10 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4514,13 +4514,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>157</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>163</v>
+        <v>231</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
@@ -4616,22 +4616,22 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>168</v>
       </c>
     </row>
     <row r="22">
@@ -4639,7 +4639,7 @@
         <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4662,13 +4662,13 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4719,7 +4719,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4743,7 +4743,7 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4757,7 +4757,7 @@
         <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4783,10 +4783,10 @@
         <v>137</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>154</v>
@@ -4830,7 +4830,7 @@
         <v>140</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
@@ -4839,7 +4839,7 @@
         <v>141</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4863,7 +4863,7 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -4877,7 +4877,7 @@
         <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4903,16 +4903,16 @@
         <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4937,31 +4937,31 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y24" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Z24" t="s" s="2">
+      <c r="AA24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4985,7 +4985,7 @@
         <v>135</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4999,7 +4999,7 @@
         <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5022,19 +5022,19 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5059,29 +5059,29 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5102,10 +5102,10 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5119,7 +5119,7 @@
         <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5145,16 +5145,16 @@
         <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5167,43 +5167,43 @@
         <v>239</v>
       </c>
       <c r="T26" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5224,10 +5224,10 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5241,7 +5241,7 @@
         <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5264,16 +5264,16 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5287,43 +5287,43 @@
         <v>82</v>
       </c>
       <c r="T27" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5344,10 +5344,10 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5361,7 +5361,7 @@
         <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5384,13 +5384,13 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5441,7 +5441,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5462,10 +5462,10 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5479,7 +5479,7 @@
         <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5502,16 +5502,16 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5561,7 +5561,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5582,10 +5582,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -6255,7 +6255,7 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y35" t="s" s="2">
         <v>287</v>
@@ -6375,7 +6375,7 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y36" t="s" s="2">
         <v>298</v>
@@ -6460,7 +6460,7 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>304</v>
@@ -6497,7 +6497,7 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
@@ -6615,7 +6615,7 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y38" t="s" s="2">
         <v>316</v>
@@ -6824,7 +6824,7 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>333</v>
@@ -6944,13 +6944,13 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7001,7 +7001,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7025,7 +7025,7 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7065,10 +7065,10 @@
         <v>137</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>154</v>
@@ -7112,7 +7112,7 @@
         <v>140</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
@@ -7121,7 +7121,7 @@
         <v>141</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7145,7 +7145,7 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7304,7 +7304,7 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>356</v>
@@ -7426,7 +7426,7 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>366</v>
@@ -7546,13 +7546,13 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7603,7 +7603,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7627,7 +7627,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7667,10 +7667,10 @@
         <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>154</v>
@@ -7714,7 +7714,7 @@
         <v>140</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
@@ -7723,7 +7723,7 @@
         <v>141</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7747,7 +7747,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7906,7 +7906,7 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>356</v>
@@ -8858,7 +8858,7 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>444</v>
@@ -9098,7 +9098,7 @@
         <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>463</v>
@@ -9334,7 +9334,7 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>473</v>
@@ -9932,7 +9932,7 @@
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>515</v>
@@ -10172,13 +10172,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10229,7 +10229,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10253,7 +10253,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10293,10 +10293,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>154</v>
@@ -10340,7 +10340,7 @@
         <v>140</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>82</v>
@@ -10349,7 +10349,7 @@
         <v>141</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10373,7 +10373,7 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10766,7 +10766,7 @@
         <v>93</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>551</v>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T08:54:25+00:00</t>
+    <t>2026-06-24T09:36:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T09:36:36+00:00</t>
+    <t>2026-06-24T12:11:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:11:25+00:00</t>
+    <t>2026-06-24T12:16:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:16:25+00:00</t>
+    <t>2026-06-25T08:27:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T08:27:57+00:00</t>
+    <t>2026-06-25T09:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T09:12:27+00:00</t>
+    <t>2026-06-25T09:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T09:43:13+00:00</t>
+    <t>2026-06-25T10:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T10:03:25+00:00</t>
+    <t>2026-06-25T10:20:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T10:20:08+00:00</t>
+    <t>2026-06-25T14:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0-ballot</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:41:02+00:00</t>
+    <t>2026-06-30T07:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
